--- a/docs/submission/Refill-Citations.xlsx
+++ b/docs/submission/Refill-Citations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\claude\refill\docs\submission\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{625B75E4-EC51-4E01-8E6B-AE77BF72B20A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49A36DFB-3D63-478E-99E4-AF6AB23FFE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1470" yWindow="1470" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Assumptions!$A$1:$F$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Citations!$A$1:$L$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Product evidence'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Product evidence'!$A$1:$F$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="516">
   <si>
     <t>Refill: citations and evidence</t>
   </si>
@@ -989,7 +989,7 @@
     <t>Fit check in src/engine.ts and in the database functions (supabase/migrations); scenario C02 in tests/core-scenarios.json; Lab case check on #/lab.</t>
   </si>
   <si>
-    <t>npm test 51/51 and npm run dbtest 28/28 passed on 18 Oct 2026.</t>
+    <t>npm test 51/51 and npm run dbtest 32/32 passed on 18 Oct 2026.</t>
   </si>
   <si>
     <t>E02</t>
@@ -1049,7 +1049,7 @@
     <t>Database rules OFFER_EXPIRED, FREQUENCY_CAP, late flag and restore_slot (supabase/migrations 002-003); Owner &gt; Rules page. These are defaults the owner can change.</t>
   </si>
   <si>
-    <t>Covered by npm run dbtest (28/28) on 18 Oct 2026.</t>
+    <t>Covered by npm run dbtest (32/32) on 18 Oct 2026.</t>
   </si>
   <si>
     <t>E06</t>
@@ -1094,7 +1094,7 @@
     <t>Functions-only API: tables have no direct client access; every action is a database function (supabase/migrations).</t>
   </si>
   <si>
-    <t>dbtest calls the live database directly and the rules still hold (28/28).</t>
+    <t>dbtest calls the live database directly and the rules still hold (32/32).</t>
   </si>
   <si>
     <t>E09</t>
@@ -1109,7 +1109,7 @@
     <t>npm test, npm run dbtest, npm run flowtest.</t>
   </si>
   <si>
-    <t>51/51, 28/28 and 14/14 on 18 Oct 2026.</t>
+    <t>51/51, 32/32 (four checks added on 18 Oct for absence cover) and 14/14 on 18 Oct 2026.</t>
   </si>
   <si>
     <t>E10</t>
@@ -1155,6 +1155,36 @@
   </si>
   <si>
     <t>Checked in the deck, film and brief.</t>
+  </si>
+  <si>
+    <t>E13</t>
+  </si>
+  <si>
+    <t>When someone is marked out, their coming appointments move automatically to a teammate who is in, does that service and is free at that time; the rest stay flagged.</t>
+  </si>
+  <si>
+    <t>Live app (owner rule 'Cover absences automatically'); README</t>
+  </si>
+  <si>
+    <t>Absence planner cover_absence_plan (supabase/migrations/012_absence_cover.sql); db-test check 12c.</t>
+  </si>
+  <si>
+    <t>npm run dbtest 32/32 on 18 Oct 2026; on the demo day, marking Arjun out moves Manav's 16:30 to Riya and flags three clients.</t>
+  </si>
+  <si>
+    <t>E14</t>
+  </si>
+  <si>
+    <t>The owner is notified of every absence with what was covered, what is left, the person's tasks and who is in; tasks can be handed over or marked missed.</t>
+  </si>
+  <si>
+    <t>Live app (Owner overview, bell); README</t>
+  </si>
+  <si>
+    <t>notices table, reassign_task and read_notice (migration 012); db-test check 12c.</t>
+  </si>
+  <si>
+    <t>npm run dbtest 32/32 on 18 Oct 2026; checked in the browser on the demo day.</t>
   </si>
   <si>
     <t>Assumption</t>
@@ -2477,7 +2507,7 @@
       </c>
       <c r="C24" s="10">
         <f>COUNTA('Product evidence'!A2:A200)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -4035,7 +4065,7 @@
     <tabColor rgb="FF3F6B00"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -4306,9 +4336,49 @@
         <v>19</v>
       </c>
     </row>
+    <row r="14" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>378</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F13" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
-  <conditionalFormatting sqref="F2:F13">
+  <autoFilter ref="A1:F15" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <conditionalFormatting sqref="F2:F15">
     <cfRule type="expression" dxfId="17" priority="1">
       <formula>$F2="Verified"</formula>
     </cfRule>
@@ -4361,16 +4431,16 @@
         <v>34</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="F1" s="11" t="s">
         <v>43</v>
@@ -4378,19 +4448,19 @@
     </row>
     <row r="2" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="F2" s="13" t="s">
         <v>23</v>
@@ -4398,19 +4468,19 @@
     </row>
     <row r="3" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>23</v>
@@ -4418,19 +4488,19 @@
     </row>
     <row r="4" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="F4" s="13" t="s">
         <v>23</v>
@@ -4438,19 +4508,19 @@
     </row>
     <row r="5" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>23</v>
@@ -4458,19 +4528,19 @@
     </row>
     <row r="6" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>23</v>
@@ -4478,19 +4548,19 @@
     </row>
     <row r="7" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>23</v>
@@ -4498,19 +4568,19 @@
     </row>
     <row r="8" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>110</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>23</v>
@@ -4518,19 +4588,19 @@
     </row>
     <row r="9" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>23</v>
@@ -4538,19 +4608,19 @@
     </row>
     <row r="10" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="F10" s="13" t="s">
         <v>23</v>
@@ -4558,19 +4628,19 @@
     </row>
     <row r="11" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>222</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="F11" s="13" t="s">
         <v>23</v>
@@ -4578,19 +4648,19 @@
     </row>
     <row r="12" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>23</v>
@@ -4598,19 +4668,19 @@
     </row>
     <row r="13" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="F13" s="13" t="s">
         <v>23</v>
@@ -4618,19 +4688,19 @@
     </row>
     <row r="14" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>23</v>
@@ -4638,19 +4708,19 @@
     </row>
     <row r="15" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>23</v>
@@ -4658,19 +4728,19 @@
     </row>
     <row r="16" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>293</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="F16" s="13" t="s">
         <v>23</v>
@@ -4726,23 +4796,23 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="D4" s="17"/>
       <c r="E4" s="17"/>
@@ -4750,29 +4820,29 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="B5" s="19">
         <v>699</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="B6" s="19">
         <v>100</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="B7" s="20">
         <v>12</v>
@@ -4781,7 +4851,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="B8" s="20">
         <v>100000</v>
@@ -4790,29 +4860,29 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="B9" s="19">
         <v>500</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="B10" s="19">
         <v>300000</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="B11" s="21">
         <v>7.0000000000000007E-2</v>
@@ -4823,7 +4893,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="B12" s="19">
         <v>300000</v>
@@ -4834,7 +4904,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="B13" s="19">
         <v>13000</v>
@@ -4845,27 +4915,27 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="B16" s="24">
         <v>50</v>
@@ -4877,7 +4947,7 @@
         <v>800</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="F16" s="26" t="str">
         <f>IF(AND(ROUND(B16,2)=50,ROUND(C16,2)=250,ROUND(D16,2)=800),"Matches","Differs")</f>
@@ -4886,7 +4956,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="23" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="B17" s="27">
         <f>B16*$B$5*$B$7/$B$8</f>
@@ -4901,7 +4971,7 @@
         <v>67.103999999999999</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="F17" s="26" t="str">
         <f>IF(AND(ROUND(B17,2)=4.19,ROUND(C17,2)=20.97,ROUND(D17,2)=67.1),"Matches","Differs")</f>
@@ -4910,7 +4980,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="23" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="B18" s="27">
         <f>B16*$B$6*$B$7/$B$8</f>
@@ -4925,7 +4995,7 @@
         <v>9.6</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="F18" s="26" t="str">
         <f>IF(AND(ROUND(B18,2)=0.6,ROUND(C18,2)=3,ROUND(D18,2)=9.6),"Matches","Differs")</f>
@@ -4934,7 +5004,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="23" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="B19" s="27">
         <f>B17-B18</f>
@@ -4949,7 +5019,7 @@
         <v>57.503999999999998</v>
       </c>
       <c r="E19" s="25" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="F19" s="26" t="str">
         <f>IF(AND(ROUND(B19,2)=3.59,ROUND(C19,2)=17.97,ROUND(D19,2)=57.5),"Matches","Differs")</f>
@@ -4958,7 +5028,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="23" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="B20" s="28">
         <v>15</v>
@@ -4970,7 +5040,7 @@
         <v>49</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="F20" s="26" t="str">
         <f>IF(AND(ROUND(B20,2)=15,ROUND(C20,2)=27,ROUND(D20,2)=49),"Matches","Differs")</f>
@@ -4979,7 +5049,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="23" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="B21" s="27">
         <f>B19-B20</f>
@@ -4994,7 +5064,7 @@
         <v>8.5039999999999978</v>
       </c>
       <c r="E21" s="25" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="F21" s="26" t="str">
         <f>IF(AND(ROUND(B21,2)=-11.41,ROUND(C21,2)=-9.03,ROUND(D21,2)=8.5),"Matches","Differs")</f>
@@ -5011,23 +5081,23 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="C23" s="22"/>
       <c r="D23" s="22"/>
       <c r="E23" s="22" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="23" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="B24" s="30">
         <f>B5-B6</f>
@@ -5036,7 +5106,7 @@
       <c r="C24" s="29"/>
       <c r="D24" s="29"/>
       <c r="E24" s="25" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="F24" s="26" t="str">
         <f>IF(B24=599,"Matches","Differs")</f>
@@ -5045,7 +5115,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="23" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="B25" s="31">
         <f>(B5-B6)/B5</f>
@@ -5054,7 +5124,7 @@
       <c r="C25" s="29"/>
       <c r="D25" s="29"/>
       <c r="E25" s="25" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="F25" s="26" t="str">
         <f>IF(ROUND(B25,2)=0.86,"Matches","Differs")</f>
@@ -5063,7 +5133,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="23" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="B26" s="30">
         <f>ROUNDUP(B20*$B$8/((B5-B6)*B7),0)</f>
@@ -5072,7 +5142,7 @@
       <c r="C26" s="29"/>
       <c r="D26" s="29"/>
       <c r="E26" s="25" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="F26" s="26" t="str">
         <f>IF(B26=209,"Matches","Differs")</f>
@@ -5081,7 +5151,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="23" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="B27" s="30">
         <f>ROUNDUP(D20*$B$8/((B5-B6)*B7),0)</f>
@@ -5090,7 +5160,7 @@
       <c r="C27" s="29"/>
       <c r="D27" s="29"/>
       <c r="E27" s="25" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="F27" s="26" t="str">
         <f>IF(B27=682,"Matches","Differs")</f>
@@ -5099,7 +5169,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="23" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="B28" s="30">
         <f>ROUNDUP(D20*$B$8/((499-B6)*B7),0)</f>
@@ -5108,7 +5178,7 @@
       <c r="C28" s="29"/>
       <c r="D28" s="29"/>
       <c r="E28" s="25" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="F28" s="26" t="str">
         <f>IF(ABS(B28-1000)&lt;=50,"Matches","Differs")</f>
@@ -5117,7 +5187,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="23" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="B29" s="30">
         <f>ROUNDUP(D20*$B$8/((999-B6)*B7),0)</f>
@@ -5126,7 +5196,7 @@
       <c r="C29" s="29"/>
       <c r="D29" s="29"/>
       <c r="E29" s="25" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="F29" s="26" t="str">
         <f>IF(ABS(B29-450)&lt;=10,"Matches","Differs")</f>
@@ -5135,7 +5205,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="23" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="B30" s="32">
         <f>B5/B9</f>
@@ -5144,7 +5214,7 @@
       <c r="C30" s="29"/>
       <c r="D30" s="29"/>
       <c r="E30" s="25" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="F30" s="26" t="str">
         <f>IF(ROUNDUP(B30,0)=2,"Matches","Differs")</f>
@@ -5153,7 +5223,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="23" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="B31" s="30">
         <f>B10*B11</f>
@@ -5162,7 +5232,7 @@
       <c r="C31" s="29"/>
       <c r="D31" s="29"/>
       <c r="E31" s="25" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="F31" s="26" t="str">
         <f>IF(ROUND(B31,0)=21000,"Matches","Differs")</f>
@@ -5171,7 +5241,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="23" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="B32" s="33">
         <f>B10*B11/6/B5</f>
@@ -5180,7 +5250,7 @@
       <c r="C32" s="29"/>
       <c r="D32" s="29"/>
       <c r="E32" s="25" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F32" s="26" t="str">
         <f>IF(ROUND(B32,0)=5,"Matches","Differs")</f>
@@ -5189,7 +5259,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="23" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="B33" s="34">
         <f>D16/B12</f>
@@ -5198,7 +5268,7 @@
       <c r="C33" s="29"/>
       <c r="D33" s="29"/>
       <c r="E33" s="25" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="F33" s="26" t="str">
         <f>IF(B33&lt;0.003,"Matches","Differs")</f>
@@ -5207,7 +5277,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="23" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="B34" s="31">
         <f>D16/B13</f>
@@ -5216,7 +5286,7 @@
       <c r="C34" s="29"/>
       <c r="D34" s="29"/>
       <c r="E34" s="25" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="F34" s="26" t="str">
         <f>IF(ROUND(B34,2)=0.06,"Matches","Differs")</f>
@@ -5225,7 +5295,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="23" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="B35" s="30">
         <f>ROUND(B16*0.7,0)</f>
@@ -5234,7 +5304,7 @@
       <c r="C35" s="29"/>
       <c r="D35" s="29"/>
       <c r="E35" s="25" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="F35" s="26" t="str">
         <f>IF(B35=35,"Matches","Differs")</f>
@@ -5243,7 +5313,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="23" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="B36" s="30">
         <f>ROUND(D16*0.7,0)</f>
@@ -5252,7 +5322,7 @@
       <c r="C36" s="29"/>
       <c r="D36" s="29"/>
       <c r="E36" s="25" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="F36" s="26" t="str">
         <f>IF(B36=560,"Matches","Differs")</f>
